--- a/DataTables/Datas/condition.xlsx
+++ b/DataTables/Datas/condition.xlsx
@@ -1,173 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D13681B-11A0-46FF-94F0-27B49FE3ADA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="condition" sheetId="1" r:id="rId1"/>
+    <sheet name="condition" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>composeType</t>
-  </si>
-  <si>
-    <t>hasItem</t>
-  </si>
-  <si>
-    <t>taskState</t>
-  </si>
-  <si>
-    <t>hasPerkId</t>
-  </si>
-  <si>
-    <t>battleId</t>
-  </si>
-  <si>
-    <t>dialogFinishId</t>
-  </si>
-  <si>
-    <t>##备注</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>list#sep=|#,list#sep=-#,int</t>
-  </si>
-  <si>
-    <t>list#sep=|#,int</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>0无条件判断仅占位
-1大于条件数量
-2等于条件数量
-3小于数量条件
-4满足部分条件
-5满住全部条件</t>
-  </si>
-  <si>
-    <t>物品id,数量</t>
-  </si>
-  <si>
-    <t>任务id,进度</t>
-  </si>
-  <si>
-    <t>战斗ID,胜负(1胜利2失败)</t>
-  </si>
-  <si>
-    <t>竖杠隔开的是后面物品、任务状态、特质三个字段对应的判断</t>
-  </si>
-  <si>
-    <t>##comment</t>
-  </si>
-  <si>
-    <t>条件唯一标识</t>
-  </si>
-  <si>
-    <t>判断</t>
-  </si>
-  <si>
-    <t>是否有某物品</t>
-  </si>
-  <si>
-    <t>某任务状态</t>
-  </si>
-  <si>
-    <t>是否有某个特质</t>
-  </si>
-  <si>
-    <t>战斗id与结果条件</t>
-  </si>
-  <si>
-    <t>需要完成对话的id</t>
-  </si>
-  <si>
-    <t>2-3|4|4|4|0</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>1|2</t>
-  </si>
-  <si>
-    <t>2002-1</t>
-  </si>
-  <si>
-    <t>0|0|0|5|0</t>
-  </si>
-  <si>
-    <t>2003-2</t>
-  </si>
-  <si>
-    <t>2004-2</t>
-  </si>
-  <si>
-    <t>0|0|0|0|5</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -186,25 +61,84 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -492,189 +426,361 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="17.125" customWidth="1"/>
-    <col min="2" max="2" width="18.75" customWidth="1"/>
-    <col min="3" max="3" width="18.125" customWidth="1"/>
-    <col min="4" max="4" width="20.5" customWidth="1"/>
-    <col min="5" max="5" width="15.75" customWidth="1"/>
-    <col min="6" max="8" width="16.625" customWidth="1"/>
-    <col min="9" max="9" width="20.25" customWidth="1"/>
+    <col width="17.125" customWidth="1" min="1" max="1"/>
+    <col width="18.75" customWidth="1" min="2" max="2"/>
+    <col width="18.125" customWidth="1" min="3" max="3"/>
+    <col width="20.5" customWidth="1" min="4" max="4"/>
+    <col width="15.75" customWidth="1" min="5" max="5"/>
+    <col width="16.625" customWidth="1" min="6" max="8"/>
+    <col width="20.25" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>composeType</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>hasItem</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>taskState</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>hasPerkId</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>battleId</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>dialogFinishId</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>##备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>list#sep=|#,list#sep=-#,int</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>list#sep=|#,list#sep=-#,int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>list#sep=|#,list#sep=-#,int</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>list#sep=|#,int</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>list#sep=|#,list#sep=-#,int</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>list#sep=|#,int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="81" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>0无条件判断仅占位
+1大于条件数量
+2等于条件数量
+3小于数量条件
+4满足部分条件
+5满住全部条件</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>物品id,数量</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>任务id,进度</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>战斗ID,胜负(1胜利2失败)</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>竖杠隔开的是后面物品、任务状态、特质三个字段对应的判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>条件唯一标识</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>判断</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>是否有某物品</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>某任务状态</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>是否有某个特质</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>战斗id与结果条件</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>需要完成对话的id</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2-3|4|4|4|0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1|2</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2002-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0|0|0|5|0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2002-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0|0|0|5|0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2003-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0|0|0|5|0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2004-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0|0|0|0|5</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1002001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2|0|0|0|0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2|0|0|0|0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0|0|0|0|5</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1002001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1-2|0|0|0|0</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="B8">
-        <v>4</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="B9">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2|0|0|0|5</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
         <v>1002001</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/DataTables/Datas/condition.xlsx
+++ b/DataTables/Datas/condition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1F7307-F89D-4724-8808-59FFBD245EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE493E0-D197-48C9-A15D-FC3D57D9467E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -152,11 +152,11 @@
     <t>2|0|0|0|5</t>
   </si>
   <si>
-    <t>2|0|0|0|0</t>
+    <t>2-1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2-1</t>
+    <t>1-2|0|0|0|0</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -516,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
@@ -759,10 +759,21 @@
         <v>11</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>41</v>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16">
+        <v>1002004</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/condition.xlsx
+++ b/DataTables/Datas/condition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE493E0-D197-48C9-A15D-FC3D57D9467E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{115B76E3-1911-4A2F-AE80-F3C5459852C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="47">
   <si>
     <t>##var</t>
   </si>
@@ -157,6 +157,26 @@
   </si>
   <si>
     <t>1-2|0|0|0|0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>教练和拳王的战斗</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>给教练报纸的分支</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>河马上台打的分支</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>河马被拳王打爆</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>拳王被河马打爆</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -516,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
@@ -662,6 +682,9 @@
       <c r="G6" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="I6" s="2" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B7">
@@ -673,6 +696,9 @@
       <c r="G7" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="I7" s="2" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B8">
@@ -684,6 +710,9 @@
       <c r="G8" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="I8" s="2" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B9">
@@ -773,7 +802,24 @@
         <v>34</v>
       </c>
       <c r="H16">
-        <v>1002004</v>
+        <v>1003004</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B17">
+        <v>13</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17">
+        <v>1003005</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
